--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/149.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/149.xlsx
@@ -426,13 +426,13 @@
         <v>-11.56456974249399</v>
       </c>
       <c r="E2">
-        <v>-9.852761431291443</v>
+        <v>-11.49039757593929</v>
       </c>
       <c r="F2">
-        <v>1.709244039647561</v>
+        <v>0.4230785633235061</v>
       </c>
       <c r="G2">
-        <v>-9.695516422359145</v>
+        <v>-5.413580698210127</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.30000571428222</v>
       </c>
       <c r="E3">
-        <v>-10.74816056723388</v>
+        <v>-11.22689293022421</v>
       </c>
       <c r="F3">
-        <v>2.202250212893298</v>
+        <v>0.4266670509124336</v>
       </c>
       <c r="G3">
-        <v>-9.417523032925105</v>
+        <v>-4.495862202520349</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.96974376910066</v>
       </c>
       <c r="E4">
-        <v>-11.50652864872492</v>
+        <v>-12.11677244831595</v>
       </c>
       <c r="F4">
-        <v>1.720214937530238</v>
+        <v>0.4437305910427006</v>
       </c>
       <c r="G4">
-        <v>-8.938955274161904</v>
+        <v>-4.320535038759545</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.60229362857502</v>
       </c>
       <c r="E5">
-        <v>-11.88717461985678</v>
+        <v>-12.4298539776155</v>
       </c>
       <c r="F5">
-        <v>2.304876650426129</v>
+        <v>0.655164743668052</v>
       </c>
       <c r="G5">
-        <v>-8.005778559748144</v>
+        <v>-4.42757556699519</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.223784266032</v>
       </c>
       <c r="E6">
-        <v>-11.2054457469428</v>
+        <v>-13.28739659233212</v>
       </c>
       <c r="F6">
-        <v>2.590491103972176</v>
+        <v>0.9544588565039303</v>
       </c>
       <c r="G6">
-        <v>-8.618408053265014</v>
+        <v>-3.855485715489127</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.845632026488829</v>
       </c>
       <c r="E7">
-        <v>-13.90279037396594</v>
+        <v>-13.96703224673839</v>
       </c>
       <c r="F7">
-        <v>1.886925534078444</v>
+        <v>0.9423414981357791</v>
       </c>
       <c r="G7">
-        <v>-7.512958746262053</v>
+        <v>-3.651654442282548</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.49308667166974</v>
       </c>
       <c r="E8">
-        <v>-14.49914168167542</v>
+        <v>-14.29495320010155</v>
       </c>
       <c r="F8">
-        <v>1.820308227545308</v>
+        <v>0.6909866636347138</v>
       </c>
       <c r="G8">
-        <v>-7.91164946888785</v>
+        <v>-3.160654317776463</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.168628317830722</v>
       </c>
       <c r="E9">
-        <v>-13.83390936414366</v>
+        <v>-14.82864085534202</v>
       </c>
       <c r="F9">
-        <v>2.59061370234779</v>
+        <v>0.967222341446265</v>
       </c>
       <c r="G9">
-        <v>-8.383179965605708</v>
+        <v>-3.384254149026952</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.892217217673227</v>
       </c>
       <c r="E10">
-        <v>-14.53432768801937</v>
+        <v>-15.21316177263995</v>
       </c>
       <c r="F10">
-        <v>2.408878177847607</v>
+        <v>1.315956734350829</v>
       </c>
       <c r="G10">
-        <v>-7.954748945970244</v>
+        <v>-3.578321237462767</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.66204868330777</v>
       </c>
       <c r="E11">
-        <v>-15.19710961086948</v>
+        <v>-15.93902266909156</v>
       </c>
       <c r="F11">
-        <v>2.814586023981915</v>
+        <v>1.67281575474205</v>
       </c>
       <c r="G11">
-        <v>-6.892557066097439</v>
+        <v>-3.251928559426375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.496976449606436</v>
       </c>
       <c r="E12">
-        <v>-15.99001995094913</v>
+        <v>-16.58548247143509</v>
       </c>
       <c r="F12">
-        <v>3.448746002664688</v>
+        <v>1.37773471851681</v>
       </c>
       <c r="G12">
-        <v>-7.019045030792286</v>
+        <v>-3.003414392542893</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.395170439600973</v>
       </c>
       <c r="E13">
-        <v>-16.17608381830144</v>
+        <v>-16.69164685932036</v>
       </c>
       <c r="F13">
-        <v>3.10569752361294</v>
+        <v>1.764976598507912</v>
       </c>
       <c r="G13">
-        <v>-6.228193057763067</v>
+        <v>-3.138006108448556</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.372417858045667</v>
       </c>
       <c r="E14">
-        <v>-16.894157443519</v>
+        <v>-17.87069786911461</v>
       </c>
       <c r="F14">
-        <v>3.605675236920638</v>
+        <v>1.912719238266815</v>
       </c>
       <c r="G14">
-        <v>-7.066059319389054</v>
+        <v>-2.578332958217827</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.422164443707407</v>
       </c>
       <c r="E15">
-        <v>-18.3244486659861</v>
+        <v>-18.93597580787651</v>
       </c>
       <c r="F15">
-        <v>3.980788161399949</v>
+        <v>2.474541205132718</v>
       </c>
       <c r="G15">
-        <v>-5.689523347767845</v>
+        <v>-2.810644844168861</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.545312733936223</v>
       </c>
       <c r="E16">
-        <v>-18.84239980351679</v>
+        <v>-19.18969133449896</v>
       </c>
       <c r="F16">
-        <v>3.775243701008502</v>
+        <v>2.75568910164287</v>
       </c>
       <c r="G16">
-        <v>-5.703613536326084</v>
+        <v>-2.793291224871731</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.72445379136226</v>
       </c>
       <c r="E17">
-        <v>-19.01881576096154</v>
+        <v>-19.88530023966052</v>
       </c>
       <c r="F17">
-        <v>4.595456655094849</v>
+        <v>2.935948475431265</v>
       </c>
       <c r="G17">
-        <v>-6.046882067399432</v>
+        <v>-2.631205757677054</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.943858582389749</v>
       </c>
       <c r="E18">
-        <v>-20.24790881400865</v>
+        <v>-20.20428348225265</v>
       </c>
       <c r="F18">
-        <v>4.876481953229387</v>
+        <v>3.383457397445642</v>
       </c>
       <c r="G18">
-        <v>-4.935952807499724</v>
+        <v>-2.482534296191516</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.178300643101206</v>
       </c>
       <c r="E19">
-        <v>-20.32859325041609</v>
+        <v>-21.17146672273342</v>
       </c>
       <c r="F19">
-        <v>4.609992846279175</v>
+        <v>3.587068448318955</v>
       </c>
       <c r="G19">
-        <v>-5.257463393150735</v>
+        <v>-2.407598094192792</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.403843787535374</v>
       </c>
       <c r="E20">
-        <v>-20.52619473882878</v>
+        <v>-21.42986291851895</v>
       </c>
       <c r="F20">
-        <v>5.566266803010147</v>
+        <v>3.910913714239005</v>
       </c>
       <c r="G20">
-        <v>-5.673287127155712</v>
+        <v>-2.066744501866224</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.597992117310252</v>
       </c>
       <c r="E21">
-        <v>-21.56253310107927</v>
+        <v>-22.68937409130911</v>
       </c>
       <c r="F21">
-        <v>5.696568995470509</v>
+        <v>4.488976652404195</v>
       </c>
       <c r="G21">
-        <v>-4.763975229049319</v>
+        <v>-1.852731324754303</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.739641236332426</v>
       </c>
       <c r="E22">
-        <v>-22.10451887254675</v>
+        <v>-22.49044772848379</v>
       </c>
       <c r="F22">
-        <v>6.169642992270084</v>
+        <v>4.657541135199867</v>
       </c>
       <c r="G22">
-        <v>-5.186224005493027</v>
+        <v>-1.905392653901649</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.817416814491242</v>
       </c>
       <c r="E23">
-        <v>-22.4913863542432</v>
+        <v>-23.22106405190233</v>
       </c>
       <c r="F23">
-        <v>6.73602263658619</v>
+        <v>4.892424712263666</v>
       </c>
       <c r="G23">
-        <v>-4.948097991337583</v>
+        <v>-1.988800722098536</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.820134734751113</v>
       </c>
       <c r="E24">
-        <v>-22.88344535009569</v>
+        <v>-23.21891684164739</v>
       </c>
       <c r="F24">
-        <v>6.55938654181764</v>
+        <v>4.937810962263051</v>
       </c>
       <c r="G24">
-        <v>-4.965362845318616</v>
+        <v>-1.848149467996899</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.751113431965981</v>
       </c>
       <c r="E25">
-        <v>-26.04768984104474</v>
+        <v>-23.2927526325802</v>
       </c>
       <c r="F25">
-        <v>6.70411889443477</v>
+        <v>5.116628976770575</v>
       </c>
       <c r="G25">
-        <v>-4.692158866836975</v>
+        <v>-2.046699204895656</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.609694004578255</v>
       </c>
       <c r="E26">
-        <v>-23.60316364699788</v>
+        <v>-23.2442763499968</v>
       </c>
       <c r="F26">
-        <v>6.604877166109778</v>
+        <v>5.034088792020826</v>
       </c>
       <c r="G26">
-        <v>-4.816790592127541</v>
+        <v>-2.443610705082608</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.410889238854221</v>
       </c>
       <c r="E27">
-        <v>-23.16541517336095</v>
+        <v>-23.58362694092589</v>
       </c>
       <c r="F27">
-        <v>6.136360846760406</v>
+        <v>5.090487358273029</v>
       </c>
       <c r="G27">
-        <v>-5.362553695176818</v>
+        <v>-2.430969479772438</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.160586699370654</v>
       </c>
       <c r="E28">
-        <v>-24.27261978044699</v>
+        <v>-24.20865201962198</v>
       </c>
       <c r="F28">
-        <v>6.736769823983515</v>
+        <v>4.953074460027035</v>
       </c>
       <c r="G28">
-        <v>-4.827828820258768</v>
+        <v>-2.281496519697429</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.878728359695696</v>
       </c>
       <c r="E29">
-        <v>-23.51788160565385</v>
+        <v>-23.72917207859318</v>
       </c>
       <c r="F29">
-        <v>6.803913972184832</v>
+        <v>4.61833284929056</v>
       </c>
       <c r="G29">
-        <v>-4.772995351611615</v>
+        <v>-2.662665229999969</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.571607875187892</v>
       </c>
       <c r="E30">
-        <v>-24.11270868480712</v>
+        <v>-23.90196228255135</v>
       </c>
       <c r="F30">
-        <v>6.245711970869163</v>
+        <v>4.94953401774747</v>
       </c>
       <c r="G30">
-        <v>-4.732487038535901</v>
+        <v>-2.656976417535933</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.257305287370249</v>
       </c>
       <c r="E31">
-        <v>-22.07952069358261</v>
+        <v>-23.58947881568257</v>
       </c>
       <c r="F31">
-        <v>6.109097618799468</v>
+        <v>4.580002632828221</v>
       </c>
       <c r="G31">
-        <v>-4.368825981461367</v>
+        <v>-2.316783343590916</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.937382076316865</v>
       </c>
       <c r="E32">
-        <v>-22.69998554624404</v>
+        <v>-22.89569732350393</v>
       </c>
       <c r="F32">
-        <v>6.00674122903995</v>
+        <v>4.464254855635047</v>
       </c>
       <c r="G32">
-        <v>-4.712791581340543</v>
+        <v>-2.115896990283114</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.625952589869009</v>
       </c>
       <c r="E33">
-        <v>-22.08923090166006</v>
+        <v>-22.89011540748337</v>
       </c>
       <c r="F33">
-        <v>5.513133661059781</v>
+        <v>4.218730070914885</v>
       </c>
       <c r="G33">
-        <v>-4.667991204157039</v>
+        <v>-2.399254154479594</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.320894127777213</v>
       </c>
       <c r="E34">
-        <v>-22.28853935992725</v>
+        <v>-23.00472327399201</v>
       </c>
       <c r="F34">
-        <v>6.150885440801092</v>
+        <v>4.328737262006658</v>
       </c>
       <c r="G34">
-        <v>-5.221262808650358</v>
+        <v>-1.899544586017555</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.033900336816834</v>
       </c>
       <c r="E35">
-        <v>-21.35665010928487</v>
+        <v>-22.73541659205615</v>
       </c>
       <c r="F35">
-        <v>5.203291117716653</v>
+        <v>4.067821410942481</v>
       </c>
       <c r="G35">
-        <v>-3.878682181181168</v>
+        <v>-2.242552042631792</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.759702648147475</v>
       </c>
       <c r="E36">
-        <v>-22.46297838878138</v>
+        <v>-21.88945313051315</v>
       </c>
       <c r="F36">
-        <v>5.698533882949949</v>
+        <v>4.119322669109333</v>
       </c>
       <c r="G36">
-        <v>-4.253994991365841</v>
+        <v>-1.853206480269886</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.506222564785177</v>
       </c>
       <c r="E37">
-        <v>-20.46171613301082</v>
+        <v>-21.44646330418429</v>
       </c>
       <c r="F37">
-        <v>6.144654461197234</v>
+        <v>4.199692531263747</v>
       </c>
       <c r="G37">
-        <v>-4.081121927520684</v>
+        <v>-0.9140067780844278</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.264009758567012</v>
       </c>
       <c r="E38">
-        <v>-20.84625366315404</v>
+        <v>-21.58931716091309</v>
       </c>
       <c r="F38">
-        <v>5.450986225032151</v>
+        <v>3.914846802667497</v>
       </c>
       <c r="G38">
-        <v>-3.600551727656097</v>
+        <v>-0.7461228471528879</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.037839432306392</v>
       </c>
       <c r="E39">
-        <v>-21.6441852357254</v>
+        <v>-21.39237187988972</v>
       </c>
       <c r="F39">
-        <v>5.934925088686844</v>
+        <v>3.846582701737595</v>
       </c>
       <c r="G39">
-        <v>-3.42216999272369</v>
+        <v>-0.5690151555809448</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.816750395077098</v>
       </c>
       <c r="E40">
-        <v>-21.24918161304361</v>
+        <v>-21.06525249631225</v>
       </c>
       <c r="F40">
-        <v>5.50082412145418</v>
+        <v>3.987151679788254</v>
       </c>
       <c r="G40">
-        <v>-3.46039390428218</v>
+        <v>-0.3041316201111819</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.605274932370867</v>
       </c>
       <c r="E41">
-        <v>-20.74780594191031</v>
+        <v>-20.32659140255752</v>
       </c>
       <c r="F41">
-        <v>5.633505385095383</v>
+        <v>4.052943932388202</v>
       </c>
       <c r="G41">
-        <v>-1.869638506726353</v>
+        <v>-0.1760067185577064</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.394741408864525</v>
       </c>
       <c r="E42">
-        <v>-19.08862293690926</v>
+        <v>-19.93061177521439</v>
       </c>
       <c r="F42">
-        <v>5.442192276684031</v>
+        <v>3.921279903917638</v>
       </c>
       <c r="G42">
-        <v>-2.985945900483753</v>
+        <v>0.5479658102809634</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.19231183408634</v>
       </c>
       <c r="E43">
-        <v>-20.02085690409159</v>
+        <v>-19.73775740734598</v>
       </c>
       <c r="F43">
-        <v>5.036138172975352</v>
+        <v>3.925251097246659</v>
       </c>
       <c r="G43">
-        <v>-3.00971672998584</v>
+        <v>0.7436358958957219</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.991975048366818</v>
       </c>
       <c r="E44">
-        <v>-17.81953445880405</v>
+        <v>-19.72703381570527</v>
       </c>
       <c r="F44">
-        <v>5.504266816380214</v>
+        <v>3.853120177280489</v>
       </c>
       <c r="G44">
-        <v>-2.227532428999117</v>
+        <v>0.7742233795252051</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.801764099049101</v>
       </c>
       <c r="E45">
-        <v>-18.98062698282974</v>
+        <v>-18.70905680072185</v>
       </c>
       <c r="F45">
-        <v>4.889757369226652</v>
+        <v>3.737206726606754</v>
       </c>
       <c r="G45">
-        <v>-2.253741693949304</v>
+        <v>1.145395548788372</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.61642059590097</v>
       </c>
       <c r="E46">
-        <v>-18.83965037761976</v>
+        <v>-19.04910513115351</v>
       </c>
       <c r="F46">
-        <v>5.22299963496406</v>
+        <v>3.614598410583594</v>
       </c>
       <c r="G46">
-        <v>-2.66834359948564</v>
+        <v>1.215102429371097</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.442605634702494</v>
       </c>
       <c r="E47">
-        <v>-18.64988599897702</v>
+        <v>-18.80180631602792</v>
       </c>
       <c r="F47">
-        <v>5.248693935064095</v>
+        <v>3.810618302577652</v>
       </c>
       <c r="G47">
-        <v>-1.26952753352387</v>
+        <v>1.487763372977786</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.276297049764312</v>
       </c>
       <c r="E48">
-        <v>-17.13012629815046</v>
+        <v>-18.62859663772594</v>
       </c>
       <c r="F48">
-        <v>5.18566345938508</v>
+        <v>3.321144287937452</v>
       </c>
       <c r="G48">
-        <v>-2.105756858291229</v>
+        <v>1.372530328215228</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.124107595357225</v>
       </c>
       <c r="E49">
-        <v>-17.52275843716577</v>
+        <v>-18.1996612785203</v>
       </c>
       <c r="F49">
-        <v>4.620909071913267</v>
+        <v>3.734623877044825</v>
       </c>
       <c r="G49">
-        <v>-1.351713773252117</v>
+        <v>1.921034713085174</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.985601511314607</v>
       </c>
       <c r="E50">
-        <v>-16.23671655043261</v>
+        <v>-17.61699895533746</v>
       </c>
       <c r="F50">
-        <v>4.852212445062167</v>
+        <v>3.208381946863966</v>
       </c>
       <c r="G50">
-        <v>-1.826984161596744</v>
+        <v>1.775470037663061</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.866969249715094</v>
       </c>
       <c r="E51">
-        <v>-16.77738990712145</v>
+        <v>-17.48613957291476</v>
       </c>
       <c r="F51">
-        <v>5.208214933558894</v>
+        <v>3.001672801904184</v>
       </c>
       <c r="G51">
-        <v>-1.631763124051657</v>
+        <v>2.201175439945402</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.768864427345991</v>
       </c>
       <c r="E52">
-        <v>-16.30251587745187</v>
+        <v>-16.9486060439875</v>
       </c>
       <c r="F52">
-        <v>4.81819967950322</v>
+        <v>3.116842378650205</v>
       </c>
       <c r="G52">
-        <v>-1.742456083970269</v>
+        <v>2.108856900459046</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.694009607911251</v>
       </c>
       <c r="E53">
-        <v>-16.23743920920313</v>
+        <v>-16.60808424746481</v>
       </c>
       <c r="F53">
-        <v>4.531963950405073</v>
+        <v>3.146893891288965</v>
       </c>
       <c r="G53">
-        <v>-1.988328177327545</v>
+        <v>2.100181396182776</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.642363818728942</v>
       </c>
       <c r="E54">
-        <v>-15.74430350933829</v>
+        <v>-16.59014237454155</v>
       </c>
       <c r="F54">
-        <v>4.882106567894396</v>
+        <v>3.103951325127838</v>
       </c>
       <c r="G54">
-        <v>-1.550642068116585</v>
+        <v>2.097181650647587</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.613392444477531</v>
       </c>
       <c r="E55">
-        <v>-16.0003199150347</v>
+        <v>-16.67528735991186</v>
       </c>
       <c r="F55">
-        <v>4.739296027651761</v>
+        <v>3.135913052997455</v>
       </c>
       <c r="G55">
-        <v>-1.573157129470346</v>
+        <v>1.665534193675872</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.606890428756623</v>
       </c>
       <c r="E56">
-        <v>-14.89843557165577</v>
+        <v>-16.85372177806047</v>
       </c>
       <c r="F56">
-        <v>4.378447589848657</v>
+        <v>3.150457527855808</v>
       </c>
       <c r="G56">
-        <v>-1.123654790240007</v>
+        <v>2.062492687265465</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.620179400086263</v>
       </c>
       <c r="E57">
-        <v>-15.474070661277</v>
+        <v>-16.44765400040933</v>
       </c>
       <c r="F57">
-        <v>4.772503620095187</v>
+        <v>3.152074501026073</v>
       </c>
       <c r="G57">
-        <v>-1.514851370517013</v>
+        <v>1.573421903012213</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.65313465031056</v>
       </c>
       <c r="E58">
-        <v>-14.01520534489508</v>
+        <v>-16.42768536035956</v>
       </c>
       <c r="F58">
-        <v>4.604629995713451</v>
+        <v>3.299323433812908</v>
       </c>
       <c r="G58">
-        <v>-2.071201042883254</v>
+        <v>1.565310319567624</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.698777746454129</v>
       </c>
       <c r="E59">
-        <v>-15.29988913152502</v>
+        <v>-15.91921600428345</v>
       </c>
       <c r="F59">
-        <v>4.20533371327681</v>
+        <v>3.084822665062392</v>
       </c>
       <c r="G59">
-        <v>-2.038198620506991</v>
+        <v>1.14199113784156</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.754611510181459</v>
       </c>
       <c r="E60">
-        <v>-15.75842858105404</v>
+        <v>-16.27008760342761</v>
       </c>
       <c r="F60">
-        <v>4.504033058317479</v>
+        <v>3.495681299707308</v>
       </c>
       <c r="G60">
-        <v>-1.682925885803704</v>
+        <v>1.697502761194054</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.81266712836377</v>
       </c>
       <c r="E61">
-        <v>-13.58994557771191</v>
+        <v>-15.95327233714704</v>
       </c>
       <c r="F61">
-        <v>4.377165277109124</v>
+        <v>3.214405834617124</v>
       </c>
       <c r="G61">
-        <v>-1.993092786206327</v>
+        <v>1.179437047511898</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.873656536838874</v>
       </c>
       <c r="E62">
-        <v>-15.1766550450947</v>
+        <v>-16.34568435596214</v>
       </c>
       <c r="F62">
-        <v>4.51070307264482</v>
+        <v>3.276473747374086</v>
       </c>
       <c r="G62">
-        <v>-2.774773213486964</v>
+        <v>0.5980842741965651</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.930763940180581</v>
       </c>
       <c r="E63">
-        <v>-13.58280620744453</v>
+        <v>-15.82708531746478</v>
       </c>
       <c r="F63">
-        <v>4.679623753423696</v>
+        <v>3.402978703660015</v>
       </c>
       <c r="G63">
-        <v>-2.536375681894046</v>
+        <v>0.1536963836202172</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.98471445926083</v>
       </c>
       <c r="E64">
-        <v>-13.90763301837069</v>
+        <v>-15.57106475855705</v>
       </c>
       <c r="F64">
-        <v>4.474786718794239</v>
+        <v>3.266187080966122</v>
       </c>
       <c r="G64">
-        <v>-2.835271997896832</v>
+        <v>0.18508014434999</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.029372858313812</v>
       </c>
       <c r="E65">
-        <v>-14.82966669853925</v>
+        <v>-15.04208684495893</v>
       </c>
       <c r="F65">
-        <v>4.518951955241898</v>
+        <v>3.245684987746834</v>
       </c>
       <c r="G65">
-        <v>-3.394086213157085</v>
+        <v>0.006343348153192207</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.066281112062575</v>
       </c>
       <c r="E66">
-        <v>-14.20666423375835</v>
+        <v>-15.49997424030996</v>
       </c>
       <c r="F66">
-        <v>4.323949298418477</v>
+        <v>3.412609303084962</v>
       </c>
       <c r="G66">
-        <v>-2.972309981484369</v>
+        <v>-0.07603869741938753</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.0888967384551</v>
       </c>
       <c r="E67">
-        <v>-15.12564530360316</v>
+        <v>-15.56459820852429</v>
       </c>
       <c r="F67">
-        <v>4.395275045269126</v>
+        <v>2.875943197507274</v>
       </c>
       <c r="G67">
-        <v>-2.659438349685353</v>
+        <v>-0.3043744193581555</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.096200304053853</v>
       </c>
       <c r="E68">
-        <v>-14.70108327592256</v>
+        <v>-14.66638319530362</v>
       </c>
       <c r="F68">
-        <v>4.16961285413329</v>
+        <v>3.143139730219477</v>
       </c>
       <c r="G68">
-        <v>-3.087710113900758</v>
+        <v>-0.6725155141510399</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.07954023484909</v>
       </c>
       <c r="E69">
-        <v>-13.55472219246604</v>
+        <v>-15.13163008112224</v>
       </c>
       <c r="F69">
-        <v>3.989000595831303</v>
+        <v>2.951935966305296</v>
       </c>
       <c r="G69">
-        <v>-3.001054279432526</v>
+        <v>-0.1372528258472207</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.038339817646921</v>
       </c>
       <c r="E70">
-        <v>-14.13952341948117</v>
+        <v>-14.8661235875486</v>
       </c>
       <c r="F70">
-        <v>4.031828847290843</v>
+        <v>3.10282143199042</v>
       </c>
       <c r="G70">
-        <v>-3.175707871088823</v>
+        <v>-0.3772977372771318</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.966512034478693</v>
       </c>
       <c r="E71">
-        <v>-13.34912161904173</v>
+        <v>-15.3468744112428</v>
       </c>
       <c r="F71">
-        <v>4.351946459898295</v>
+        <v>3.155268685731268</v>
       </c>
       <c r="G71">
-        <v>-3.135110792697011</v>
+        <v>-0.2740532316769658</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.86705981003793</v>
       </c>
       <c r="E72">
-        <v>-13.88750655629057</v>
+        <v>-15.49246938744599</v>
       </c>
       <c r="F72">
-        <v>4.168678455702933</v>
+        <v>2.760006552546261</v>
       </c>
       <c r="G72">
-        <v>-2.991496343484461</v>
+        <v>-0.3235868888041581</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.738860890663874</v>
       </c>
       <c r="E73">
-        <v>-13.89753656164003</v>
+        <v>-15.53072046374766</v>
       </c>
       <c r="F73">
-        <v>3.933367441059288</v>
+        <v>2.7530051912578</v>
       </c>
       <c r="G73">
-        <v>-2.558948179628811</v>
+        <v>-0.0007030514982225511</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.591060548343822</v>
       </c>
       <c r="E74">
-        <v>-15.77268655553217</v>
+        <v>-15.27344148180851</v>
       </c>
       <c r="F74">
-        <v>3.879497052120431</v>
+        <v>2.706560287717637</v>
       </c>
       <c r="G74">
-        <v>-2.598017972434822</v>
+        <v>-0.1811394424238351</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.427701924438414</v>
       </c>
       <c r="E75">
-        <v>-14.03297693615402</v>
+        <v>-15.71119826186809</v>
       </c>
       <c r="F75">
-        <v>3.931561600121185</v>
+        <v>2.93701209917646</v>
       </c>
       <c r="G75">
-        <v>-2.476537415865729</v>
+        <v>-0.284637190249339</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.260974449130874</v>
       </c>
       <c r="E76">
-        <v>-13.73027012874389</v>
+        <v>-15.42457684191902</v>
       </c>
       <c r="F76">
-        <v>3.682125264525004</v>
+        <v>2.775881385453511</v>
       </c>
       <c r="G76">
-        <v>-3.433482349036984</v>
+        <v>-0.4261682652781814</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.095238181521393</v>
       </c>
       <c r="E77">
-        <v>-13.92145905887105</v>
+        <v>-16.00176523257574</v>
       </c>
       <c r="F77">
-        <v>3.884533525929452</v>
+        <v>2.393690889884681</v>
       </c>
       <c r="G77">
-        <v>-2.711243354606814</v>
+        <v>0.1632256013777807</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.940816323844825</v>
       </c>
       <c r="E78">
-        <v>-15.36839219911674</v>
+        <v>-16.60288442688612</v>
       </c>
       <c r="F78">
-        <v>3.497709143109361</v>
+        <v>2.290559148236142</v>
       </c>
       <c r="G78">
-        <v>-1.686510438127302</v>
+        <v>0.4403169785555893</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.799136496322874</v>
       </c>
       <c r="E79">
-        <v>-15.8078019572836</v>
+        <v>-16.79650298563831</v>
       </c>
       <c r="F79">
-        <v>3.341245451333785</v>
+        <v>2.091883510348709</v>
       </c>
       <c r="G79">
-        <v>-1.496403849236206</v>
+        <v>0.8233549819853661</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.677068945058653</v>
       </c>
       <c r="E80">
-        <v>-15.40767742503829</v>
+        <v>-16.94845652837981</v>
       </c>
       <c r="F80">
-        <v>3.312146561208244</v>
+        <v>2.139433456004206</v>
       </c>
       <c r="G80">
-        <v>-1.482992454271657</v>
+        <v>0.8121783843908101</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.573192142617458</v>
       </c>
       <c r="E81">
-        <v>-17.08141743573287</v>
+        <v>-17.39995213150192</v>
       </c>
       <c r="F81">
-        <v>3.711991222865537</v>
+        <v>2.01150039431585</v>
       </c>
       <c r="G81">
-        <v>-1.374053914718273</v>
+        <v>1.142474125590916</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.491210347634899</v>
       </c>
       <c r="E82">
-        <v>-15.98380674680718</v>
+        <v>-18.11902252743743</v>
       </c>
       <c r="F82">
-        <v>2.147584591247753</v>
+        <v>2.037347114018001</v>
       </c>
       <c r="G82">
-        <v>-1.330953132263584</v>
+        <v>0.9166969333514394</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.427868541723192</v>
       </c>
       <c r="E83">
-        <v>-17.45393141909071</v>
+        <v>-18.57622464291986</v>
       </c>
       <c r="F83">
-        <v>2.450301518191999</v>
+        <v>1.841837496344067</v>
       </c>
       <c r="G83">
-        <v>-1.18029489414421</v>
+        <v>1.492799499294044</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.38352724436758</v>
       </c>
       <c r="E84">
-        <v>-19.93266346160886</v>
+        <v>-20.02735252660363</v>
       </c>
       <c r="F84">
-        <v>3.15300558598682</v>
+        <v>1.415612646377221</v>
       </c>
       <c r="G84">
-        <v>-0.6254516214070407</v>
+        <v>1.164122419740428</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.354419809197837</v>
       </c>
       <c r="E85">
-        <v>-19.74387093441613</v>
+        <v>-20.58830601419159</v>
       </c>
       <c r="F85">
-        <v>3.278057585848239</v>
+        <v>1.675784623513684</v>
       </c>
       <c r="G85">
-        <v>-0.9306894360216417</v>
+        <v>1.482513165605057</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.339284537694966</v>
       </c>
       <c r="E86">
-        <v>-19.8516592279294</v>
+        <v>-21.0652608027349</v>
       </c>
       <c r="F86">
-        <v>2.515124580930672</v>
+        <v>1.396454165085274</v>
       </c>
       <c r="G86">
-        <v>-0.4633008855975856</v>
+        <v>1.578692996341671</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.334887716642894</v>
       </c>
       <c r="E87">
-        <v>-21.36562519895783</v>
+        <v>-22.48110300300293</v>
       </c>
       <c r="F87">
-        <v>2.092362306707527</v>
+        <v>1.155332981478393</v>
       </c>
       <c r="G87">
-        <v>-0.9128554397197468</v>
+        <v>1.728160734927497</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.338114011399839</v>
       </c>
       <c r="E88">
-        <v>-23.29957220557556</v>
+        <v>-23.52768318438045</v>
       </c>
       <c r="F88">
-        <v>1.991443962759269</v>
+        <v>0.687693074841183</v>
       </c>
       <c r="G88">
-        <v>-0.0002905538528266519</v>
+        <v>1.55127756739039</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.346180113879619</v>
       </c>
       <c r="E89">
-        <v>-23.8212944589892</v>
+        <v>-24.41112937813002</v>
       </c>
       <c r="F89">
-        <v>2.045967105211532</v>
+        <v>0.8855022404252881</v>
       </c>
       <c r="G89">
-        <v>-0.6599421682002383</v>
+        <v>1.923123308758064</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.356376461647633</v>
       </c>
       <c r="E90">
-        <v>-24.99030300380002</v>
+        <v>-25.24473288277034</v>
       </c>
       <c r="F90">
-        <v>2.098749019383111</v>
+        <v>0.5808419635540748</v>
       </c>
       <c r="G90">
-        <v>-0.1632871709098024</v>
+        <v>1.725907662345367</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.369993078624956</v>
       </c>
       <c r="E91">
-        <v>-27.35466391285503</v>
+        <v>-26.90810647799814</v>
       </c>
       <c r="F91">
-        <v>1.732781271030706</v>
+        <v>0.1300858413207238</v>
       </c>
       <c r="G91">
-        <v>-0.6339417628173412</v>
+        <v>1.788821385502015</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.386664809233974</v>
       </c>
       <c r="E92">
-        <v>-28.97985911297935</v>
+        <v>-28.39702650813219</v>
       </c>
       <c r="F92">
-        <v>1.862468814878191</v>
+        <v>-0.04656019385665956</v>
       </c>
       <c r="G92">
-        <v>-1.081449493180069</v>
+        <v>1.480790074174922</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.411509260580454</v>
       </c>
       <c r="E93">
-        <v>-30.6938665840738</v>
+        <v>-29.74216651541199</v>
       </c>
       <c r="F93">
-        <v>1.729769327154127</v>
+        <v>-0.1901311753750643</v>
       </c>
       <c r="G93">
-        <v>-0.9716702938683469</v>
+        <v>1.483092750904284</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.445939441086003</v>
       </c>
       <c r="E94">
-        <v>-31.42532808599694</v>
+        <v>-32.31463238432019</v>
       </c>
       <c r="F94">
-        <v>0.9851217042859567</v>
+        <v>-0.4313981516448371</v>
       </c>
       <c r="G94">
-        <v>-0.4247245235192957</v>
+        <v>1.677285155080473</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.496142608592465</v>
       </c>
       <c r="E95">
-        <v>-33.85201208419234</v>
+        <v>-34.26271276907632</v>
       </c>
       <c r="F95">
-        <v>0.7656407907098109</v>
+        <v>-0.8088189077083479</v>
       </c>
       <c r="G95">
-        <v>-1.532437346082752</v>
+        <v>1.337924908660021</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.563736336570741</v>
       </c>
       <c r="E96">
-        <v>-37.39970804052317</v>
+        <v>-35.89021715469724</v>
       </c>
       <c r="F96">
-        <v>0.5456090128108034</v>
+        <v>-0.8260207851948823</v>
       </c>
       <c r="G96">
-        <v>-0.4785267480529583</v>
+        <v>1.247587924318319</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.650430609224944</v>
       </c>
       <c r="E97">
-        <v>-37.4754480788484</v>
+        <v>-38.37038413172812</v>
       </c>
       <c r="F97">
-        <v>-0.4133256600179603</v>
+        <v>-1.562922344479475</v>
       </c>
       <c r="G97">
-        <v>-2.011490703339902</v>
+        <v>0.8291873854019132</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.756753524782668</v>
       </c>
       <c r="E98">
-        <v>-40.74764906836938</v>
+        <v>-40.24340768142194</v>
       </c>
       <c r="F98">
-        <v>0.1864289069569378</v>
+        <v>-1.60961658660788</v>
       </c>
       <c r="G98">
-        <v>-1.104964469712227</v>
+        <v>0.3870734533644249</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.875049276769686</v>
       </c>
       <c r="E99">
-        <v>-42.87333738222047</v>
+        <v>-41.82730542473783</v>
       </c>
       <c r="F99">
-        <v>-0.0260647275765942</v>
+        <v>-1.683802686100396</v>
       </c>
       <c r="G99">
-        <v>-1.788180664739027</v>
+        <v>-0.06602649191246808</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.007625162225742</v>
       </c>
       <c r="E100">
-        <v>-45.0390522702146</v>
+        <v>-43.70755971534818</v>
       </c>
       <c r="F100">
-        <v>-0.4347861743222871</v>
+        <v>-2.236316288461041</v>
       </c>
       <c r="G100">
-        <v>-2.039177649728658</v>
+        <v>-0.01499165664538556</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.132636800795206</v>
       </c>
       <c r="E101">
-        <v>-46.70096393505607</v>
+        <v>-45.66143071499395</v>
       </c>
       <c r="F101">
-        <v>-0.8910559099886716</v>
+        <v>-2.557563794205911</v>
       </c>
       <c r="G101">
-        <v>-2.421236623936768</v>
+        <v>-0.3933929776813452</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.268388292294173</v>
       </c>
       <c r="E102">
-        <v>-49.92878578496558</v>
+        <v>-47.89469550858075</v>
       </c>
       <c r="F102">
-        <v>-1.260646108993519</v>
+        <v>-2.773292203447375</v>
       </c>
       <c r="G102">
-        <v>-3.024433497245945</v>
+        <v>-1.108413263317087</v>
       </c>
     </row>
   </sheetData>
